--- a/docs/public/downloads/opening-schedule.xlsx
+++ b/docs/public/downloads/opening-schedule.xlsx
@@ -11,135 +11,135 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="67">
   <si>
     <t>開設スケジュール</t>
   </si>
   <si>
+    <t>120日前</t>
+  </si>
+  <si>
+    <t>確認</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>☐</t>
+  </si>
+  <si>
+    <t>開設意思決定・体制確認</t>
+  </si>
+  <si>
+    <t>サビ管候補者のリストアップ・確認開始</t>
+  </si>
+  <si>
+    <t>物件候補探し開始（エリア・条件の整理）・上位店へ候補提出（1件以上）</t>
+  </si>
+  <si>
+    <t>作業提供先のリストアップ</t>
+  </si>
+  <si>
+    <t>開設資金の概算確認・資金計画のたたき台作成</t>
+  </si>
+  <si>
+    <t>採用計画の策定（必要職種・人数・時期）</t>
+  </si>
+  <si>
+    <t>上位店への進捗共有</t>
+  </si>
+  <si>
     <t>90日前</t>
   </si>
   <si>
-    <t>確認</t>
-  </si>
-  <si>
-    <t>項目</t>
-  </si>
-  <si>
-    <t>☐</t>
-  </si>
-  <si>
-    <t>開設意思決定・体制確認</t>
-  </si>
-  <si>
-    <t>サビ管候補者のリストアップ・確認開始</t>
-  </si>
-  <si>
-    <t>物件候補探し開始（エリア・条件の整理）</t>
-  </si>
-  <si>
-    <t>作業提供先のリストアップ</t>
-  </si>
-  <si>
-    <t>開設資金の概算確認・資金計画のたたき台作成</t>
-  </si>
-  <si>
-    <t>採用計画の策定（必要職種・人数・時期）</t>
-  </si>
-  <si>
-    <t>上位店への進捗共有</t>
+    <t>サビ管候補者との面談実施</t>
+  </si>
+  <si>
+    <t>作業発注元との商談開始</t>
+  </si>
+  <si>
+    <t>採用開始（求人掲載・募集）</t>
+  </si>
+  <si>
+    <t>備品リスト作成</t>
+  </si>
+  <si>
+    <t>送迎用車両・弁当手配業者の候補リストアップ</t>
+  </si>
+  <si>
+    <t>内装・レイアウトの検討開始</t>
+  </si>
+  <si>
+    <t>利用者募集の準備開始（パンフレット案・見学導線）</t>
   </si>
   <si>
     <t>60日前</t>
   </si>
   <si>
-    <t>サビ管候補者との面談実施</t>
-  </si>
-  <si>
-    <t>上位店へ物件候補提出（1件以上）</t>
-  </si>
-  <si>
-    <t>作業発注元との商談開始</t>
-  </si>
-  <si>
-    <t>採用開始（求人掲載・募集）</t>
-  </si>
-  <si>
-    <t>備品リスト作成</t>
-  </si>
-  <si>
-    <t>送迎用車両・弁当手配業者の候補リストアップ</t>
-  </si>
-  <si>
-    <t>内装・レイアウトの検討開始</t>
-  </si>
-  <si>
-    <t>利用者募集の準備開始（パンフレット案・見学導線）</t>
-  </si>
-  <si>
-    <t>30日前</t>
-  </si>
-  <si>
     <t>サビ管の雇用条件合意・勤務開始日調整</t>
   </si>
   <si>
     <t>物件の最終選定結果を上位店から確認</t>
   </si>
   <si>
+    <t>主要職員（管理者・生援・職指）の採用決定</t>
+  </si>
+  <si>
+    <t>指定申請に必要な資料の準備（上位店の指示に従う）</t>
+  </si>
+  <si>
+    <t>IT環境整備開始（HP・SNS・電話・メール）</t>
+  </si>
+  <si>
+    <t>運転資金の最終確認</t>
+  </si>
+  <si>
+    <t>弁当手配業者の見積・試食</t>
+  </si>
+  <si>
+    <t>45日前</t>
+  </si>
+  <si>
     <t>作業発注元との契約・単価・作業量の確定</t>
   </si>
   <si>
-    <t>主要職員（管理者・生援・職指）の採用決定</t>
-  </si>
-  <si>
-    <t>指定申請に必要な資料の準備（上位店の指示に従う）</t>
-  </si>
-  <si>
-    <t>IT環境整備開始（HP・SNS・電話・メール）</t>
-  </si>
-  <si>
     <t>市役所・相談支援事業所等への案内用名刺を準備</t>
   </si>
   <si>
+    <t>送迎用車両の手配方針を上位店と確認</t>
+  </si>
+  <si>
+    <t>14日前</t>
+  </si>
+  <si>
+    <t>サビ管・主要職員の雇用契約書兼労働条件通知書の締結</t>
+  </si>
+  <si>
+    <t>物件契約・内装工事の進捗確認（契約前は上位店のアドバイスを受ける）</t>
+  </si>
+  <si>
+    <t>作業マニュアル・検品ルールの作成</t>
+  </si>
+  <si>
+    <t>備品の発注・納品スケジュール確認</t>
+  </si>
+  <si>
+    <t>送迎用車両の確保・保険・点検の完了</t>
+  </si>
+  <si>
+    <t>弁当手配業者の契約・注文ルールの確定</t>
+  </si>
+  <si>
+    <t>見学・体験利用の受付体制整備</t>
+  </si>
+  <si>
+    <t>指定申請の進捗確認（上位店と連携）</t>
+  </si>
+  <si>
+    <t>職員研修の日程確定</t>
+  </si>
+  <si>
     <t>利用者募集の営業活動開始（相談支援事業所等）</t>
-  </si>
-  <si>
-    <t>運転資金の最終確認</t>
-  </si>
-  <si>
-    <t>送迎用車両の手配方針を上位店と確認</t>
-  </si>
-  <si>
-    <t>弁当手配業者の見積・試食</t>
-  </si>
-  <si>
-    <t>14日前</t>
-  </si>
-  <si>
-    <t>サビ管・主要職員の雇用契約書兼労働条件通知書の締結</t>
-  </si>
-  <si>
-    <t>物件契約・内装工事の進捗確認（契約前は必ず上位店確認）</t>
-  </si>
-  <si>
-    <t>作業マニュアル・検品ルールの作成</t>
-  </si>
-  <si>
-    <t>備品の発注・納品スケジュール確認</t>
-  </si>
-  <si>
-    <t>送迎用車両の確保・保険・点検の完了</t>
-  </si>
-  <si>
-    <t>弁当手配業者の契約・注文ルールの確定</t>
-  </si>
-  <si>
-    <t>見学・体験利用の受付体制整備</t>
-  </si>
-  <si>
-    <t>指定申請の進捗確認（上位店と連携）</t>
-  </si>
-  <si>
-    <t>職員研修の日程確定</t>
   </si>
   <si>
     <t>7日前</t>
@@ -654,7 +654,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -807,26 +807,26 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="5" t="s">
+    <row r="22" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -877,28 +877,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="5" t="s">
+    <row r="32" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="B32" s="2"/>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>30</v>
+      <c r="A33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -906,7 +896,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -914,29 +904,29 @@
         <v>4</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B37" s="2"/>
-    </row>
-    <row r="38" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -944,7 +934,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -952,7 +942,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -960,7 +950,7 @@
         <v>4</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -968,7 +958,7 @@
         <v>4</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -976,7 +966,7 @@
         <v>4</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -984,7 +974,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -992,7 +982,7 @@
         <v>4</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1000,37 +990,37 @@
         <v>4</v>
       </c>
       <c r="B47" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="49" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+    <row r="51" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="2"/>
-    </row>
-    <row r="50" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B51" s="2"/>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B52" s="3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1038,7 +1028,7 @@
         <v>4</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1046,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1054,7 +1044,7 @@
         <v>4</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1062,7 +1052,7 @@
         <v>4</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1070,7 +1060,7 @@
         <v>4</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1078,37 +1068,37 @@
         <v>4</v>
       </c>
       <c r="B58" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="60" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+    <row r="62" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B60" s="2"/>
-    </row>
-    <row r="61" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+      <c r="B62" s="2"/>
+    </row>
+    <row r="63" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B63" s="3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1116,7 +1106,7 @@
         <v>4</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1124,7 +1114,7 @@
         <v>4</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1132,7 +1122,7 @@
         <v>4</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1140,7 +1130,7 @@
         <v>4</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1148,37 +1138,37 @@
         <v>4</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="70" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
+    <row r="72" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="2"/>
-    </row>
-    <row r="71" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
+      <c r="B72" s="2"/>
+    </row>
+    <row r="73" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1186,7 +1176,7 @@
         <v>4</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1194,7 +1184,7 @@
         <v>4</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1202,7 +1192,7 @@
         <v>4</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1210,19 +1200,36 @@
         <v>4</v>
       </c>
       <c r="B77" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A72:B72"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>

--- a/docs/public/downloads/opening-schedule.xlsx
+++ b/docs/public/downloads/opening-schedule.xlsx
@@ -73,19 +73,19 @@
     <t>利用者募集の準備開始（パンフレット案・見学導線）</t>
   </si>
   <si>
+    <t>指定申請に必要な資料の準備（上位店の指示に従う）</t>
+  </si>
+  <si>
     <t>60日前</t>
   </si>
   <si>
     <t>サビ管の雇用条件合意・勤務開始日調整</t>
   </si>
   <si>
-    <t>物件の最終選定結果を上位店から確認</t>
+    <t>物件の最終選定結果を上位店へ報告</t>
   </si>
   <si>
     <t>主要職員（管理者・生援・職指）の採用決定</t>
-  </si>
-  <si>
-    <t>指定申請に必要な資料の準備（上位店の指示に従う）</t>
   </si>
   <si>
     <t>IT環境整備開始（HP・SNS・電話・メール）</t>
@@ -807,26 +807,26 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1224,7 +1224,7 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A51:B51"/>
